--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,70 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II: Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff2428319ab1fc</t>
+          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,103 +468,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Ashburn, VA, US USA</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>10.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,138 +468,173 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Sr Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Code360 Inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=e4b86ec80ea1ccc1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Ashburn, VA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>10.4</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,110 +531,145 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>VBEST Software Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ashburn, VA, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>10.4</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Architect</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Code360 Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4b86ec80ea1ccc1</t>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Doble Engineering Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, Scala, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,42 +636,112 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=0ee2aec48a20d562</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Senior Software Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Ashburn, VA, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,60 +573,60 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VBEST Software Inc</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, IAM, Databricks, Spark, Scala, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=539879c923ff55f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer AI</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Doble Engineering Company</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, Spark, Scala, PostgreSQL, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ee2aec48a20d562</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -705,41 +705,6 @@
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Data Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,19 +496,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.4</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,40 +671,215 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Oracle CX Solution Architect(Functional)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Remote</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Warehouse Analyst</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D13" t="n">
         <v>10.4</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Teleflex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=0d76a58347bab72d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,40 +846,320 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>Data Warehouse Analyst</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Smart Tech Skills LLC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Engineer - Data Services</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Crown Equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New Bremen, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DL Engineer 2 - $75-77 /hr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Evolve Blue</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DL Engineer 1 – $65-$68/hr</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Evolve Blue</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D21" t="n">
         <v>10.4</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=19d01f1d0ef0bb8a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Software Engineer III (Java)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d76a58347bab72d</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Remote</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57ea84787b8db583</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,15 +1151,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Databricks, Hadoop, HDFS, Hive, Sqoop, HBase, Oozie</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d01f1d0ef0bb8a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
@@ -888,25 +888,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RiPSIM Technologies, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
         </is>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>S R International Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,15 +1221,50 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III (Java)</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,19 +741,19 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04e8bc1c932c3a0e</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,40 +1231,215 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D29" t="n">
         <v>10.4</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,15 +968,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,497 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Data Engineer - Data Services</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Crown Equipment</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>New Bremen, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DL Engineer 2 - $75-77 /hr</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Evolve Blue</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DL Engineer 1 – $65-$68/hr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Evolve Blue</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Thales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SRE / Infrastructure Engineer (LABGEN)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MEDFAR Solutions Cliniques</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Great Neck, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Jenkins, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e01cbe5941f4fd7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Backend Software Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Cornell University</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ithaca, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Senior Full Stack Data Engineer</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Optum</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D40" t="n">
         <v>10.4</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>AI/ML Solutions Architect - MySQL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Applied Information Sciences</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>26.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, RDS, Azure, Databricks, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
+          <t>https://www.indeed.com/viewjob?jk=a67ae1ade25d4115</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (Remote)</t>
+          <t>Data Engineer - Databricks</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Teleflex</t>
+          <t>Resultant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>25</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Photon, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
+          <t>https://www.indeed.com/viewjob?jk=62b7232e7951bd03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Applied Information Sciences</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Redshift, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=4dd470eb429ea88c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Teleflex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, GCP, Cloud Storage, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd3c383bbc14178</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer (PySpark)</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SRE / Infrastructure Engineer (LABGEN)</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MEDFAR Solutions Cliniques</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Great Neck, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Jenkins, Git, Datadog</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01cbe5941f4fd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>SRE / Infrastructure Engineer (LABGEN)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>MEDFAR Solutions Cliniques</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Great Neck, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Jenkins, Git, Datadog</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=e01cbe5941f4fd7e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=af12bc7187e4862c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,15 +1886,260 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>

--- a/results/job_matches_2026-08-10.xlsx
+++ b/results/job_matches_2026-08-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Thomson Reuters</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
+          <t>AWS, Lambda, SQS, SNS, RDS, Azure, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
+          <t>https://www.indeed.com/viewjob?jk=262610840711ef87</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Data Architect</t>
+          <t>Data Reporting Analyst / Atlanta - GA / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ComplexCare Solutions</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, Data Factory, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
+          <t>https://www.indeed.com/viewjob?jk=a0063b8d48d4bc73</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Murex</t>
+          <t>Senior Software Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>ComplexCare Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hive, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
+          <t>https://www.indeed.com/viewjob?jk=ace8de476d10f3c8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer - Murex</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, Glue, API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
+          <t>https://www.indeed.com/viewjob?jk=445d7e164b6dba34</t>
         </is>
       </c>
     </row>
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
+          <t>https://www.indeed.com/viewjob?jk=adf0da1fb174a58c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Senior AWS DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c6efcd93779699f4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mindful Support Services</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mountlake Terrace, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Blob Storage, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
+          <t>https://www.indeed.com/viewjob?jk=94fe4f8fe65e0d89</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
+          <t>Data Engineer (PySpark)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Artic Consulting, Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Hadoop, HDFS, MapReduce, HBase, Zookeeper, YARN, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
+          <t>https://www.indeed.com/viewjob?jk=6551997fe759dea8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
+          <t>https://www.indeed.com/viewjob?jk=e99ba182189de9eb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Senior Database Engineer - Mountlake Terrace, WA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mindful Support Services</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountlake Terrace, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
+          <t>https://www.indeed.com/viewjob?jk=28448befb25ceef2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer - Cybersecurity</t>
+          <t>Senior Data Engineer (Microsoft Fabric &amp; AI)-Redmond</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UnitedHealth Group</t>
+          <t>Artic Consulting, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, Dataflow, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
+          <t>https://www.indeed.com/viewjob?jk=734fb1ee3423bbe6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hiring Data Engineers in USA</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Emerging Business)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>V4C.ai</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
+          <t>https://www.indeed.com/viewjob?jk=34861f28281f78de</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Native BUilder - Bangladesh</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
+          <t>https://www.indeed.com/viewjob?jk=96cc91af6b068eda</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Full Stack Developer - Cybersecurity</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cushman &amp; Wakefield</t>
+          <t>UnitedHealth Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Scala, Kafka, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a32054447bc409c</t>
+          <t>https://www.indeed.com/viewjob?jk=f5715f54542e2479</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Oracle CX Solution Architect(Functional)</t>
+          <t>Sr Engineer - ADAS Tools and Ground Truth</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Magna International</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rochester Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae2204e7b44e00e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Hiring Data Engineers in USA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>V4C.ai</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
+          <t>https://www.indeed.com/viewjob?jk=9c12be1bf8cf78dc</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
+          <t>AI Native BUilder - Bangladesh</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
+          <t>https://www.indeed.com/viewjob?jk=f2cb68ac3850d624</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
+          <t>Oracle CX Solution Architect(Functional)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,15 +1213,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
+          <t>https://www.indeed.com/viewjob?jk=acfaa14f0d5a24a9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alpha Nodus, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
+          <t>https://www.indeed.com/viewjob?jk=911e6129869c725a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
+          <t>https://www.indeed.com/viewjob?jk=84e9c84b336915c6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Full Stack AWS Engineer - Onsite Jersey City, NJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
+          <t>https://www.indeed.com/viewjob?jk=da7c944ea56b4625</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer - Storage</t>
+          <t>Senior Cloud Administrator / Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lambda</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Oracle, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
+          <t>https://www.indeed.com/viewjob?jk=bb77a486f23c08d0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
+          <t>Data Engineer Intern (Monetization Data) - 2027 Summer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
+          <t>https://www.indeed.com/viewjob?jk=f08a32ca1839a36f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Warehouse Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
+          <t>https://www.indeed.com/viewjob?jk=ab81dbb9740baeab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Alpine Bank</t>
+          <t>Alpha Nodus, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rifle, CO, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, API Gateway, IAM, PostgreSQL, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
+          <t>https://www.indeed.com/viewjob?jk=50c2ed9fef976be3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Systems Engineer (Supply Chain)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>AutoZone</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>API Gateway, ECS, RDS, GCP, Scala, Kafka, Oracle, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0c167b0b4e8118</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer Associate III - Databricks</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD, GitHub Actions, AKS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
+          <t>https://www.indeed.com/viewjob?jk=757ec134ea689644</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Services</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Crown Equipment</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Bremen, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
+          <t>https://www.indeed.com/viewjob?jk=49363362b6789db3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DL Engineer 2 - $75-77 /hr</t>
+          <t>Senior Site Reliability Engineer - Storage</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Lambda</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Lambda, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
+          <t>https://www.indeed.com/viewjob?jk=d9e2bb604f3f45fc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DL Engineer 1 – $65-$68/hr</t>
+          <t>Senior Hybrid Cloud Architect - (Data Center)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Evolve Blue</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
+          <t>https://www.indeed.com/viewjob?jk=27fc07398bd2410b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Warehouse Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Thales</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
+          <t>https://www.indeed.com/viewjob?jk=a603293fd9b8d480</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MAPDEVS CORP.</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1c9a594ddf538eb2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Architect</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sonos</t>
+          <t>Alpine Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rifle, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Spark, PySpark, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
+          <t>https://www.indeed.com/viewjob?jk=593b347235e92032</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
+          <t>Software Engineer Associate III - Databricks</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ff3b78bfd12f1d3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SRE / Infrastructure Engineer (LABGEN)</t>
+          <t>Data Engineer - Data Services</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MEDFAR Solutions Cliniques</t>
+          <t>Crown Equipment</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Great Neck, NY, US USA</t>
+          <t>New Bremen, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Jenkins, Git, Datadog</t>
+          <t>RDS, Data Factory, Dataflow, Spark, PySpark, Scala, Data Modeling, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01cbe5941f4fd7e</t>
+          <t>https://www.indeed.com/viewjob?jk=6962de5bbb6d5774</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>DL Engineer 2 - $75-77 /hr</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Zoom Communications</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af12bc7187e4862c</t>
+          <t>https://www.indeed.com/viewjob?jk=06bfd64cec5eb49c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Backend Software Engineer</t>
+          <t>DL Engineer 1 – $65-$68/hr</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Evolve Blue</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+          <t>https://www.indeed.com/viewjob?jk=e6ef460e64e2f58d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RiPSIM Technologies, Inc.</t>
+          <t>Thales</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, GCP, Scala, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe7b94fd9c87316</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GIS Architect (UI mobile responsive design) - Transportation, Rail Operations</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>MAPDEVS CORP.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+          <t>S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+          <t>https://www.indeed.com/viewjob?jk=8db4a101ed6572fd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Infrastructure Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sonos</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=08280de9f61ce7c2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. Specialist Solutions Architect - Cloud Platform &amp; Infrastructure (Azure)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>S R International Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Kafka, Terraform, Azure Monitor</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+          <t>https://www.indeed.com/viewjob?jk=4a006cef06875af1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Full Stack Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Zoom Communications</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, S3, IAM, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+          <t>https://www.indeed.com/viewjob?jk=af12bc7187e4862c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Full Stack AI Software Engineer</t>
+          <t>SRE / Infrastructure Engineer (LABGEN)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>MEDFAR Solutions Cliniques</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Great Neck, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Jenkins, Git, Datadog</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e01cbe5941f4fd7e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Backend Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ASSA ABLOY Group</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New Haven, CT, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,15 +2131,295 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, ELT, Jenkins, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9806c00941f64154</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RiPSIM Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ashburn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f4fed38dc2178d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Step Functions, Azure, GCP, Hadoop, Spark, Scala, Kafka, Airflow</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef0e8dc68e7083df</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f12a476a0f8fc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Logic, Inc.</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Scala, MLOps, Git, Python, SQL, Scala</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b3a8a9af3d57a0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Enterprise Data Architect</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>S R International Inc</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=176a4cab35257149</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97b1838bbabdfd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Full Stack AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Marlton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Data Modeling, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd8a1448552467aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>ASSA ABLOY Group</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>New Haven, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Maven, Docker, SonarQube</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8fa117edc727447d</t>
         </is>
